--- a/config/路网表头映射关系.xlsx
+++ b/config/路网表头映射关系.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>中文表头</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -454,11 +449,6 @@
           <t>起点</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>原数据保留</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -476,11 +466,6 @@
           <t>终点</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>原数据保留</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -498,11 +483,6 @@
           <t>长度</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>原数据保留</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -520,11 +500,6 @@
           <t>机动车道数</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>已有的数据保留，空白的地方则根据映射后的道路等级填充，映射关系详见《路网字段属性映射关系》</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -538,11 +513,6 @@
           <t>机动车道宽度</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>根据映射后的道路等级填充，映射关系详见《路网字段属性映射关系》</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -556,11 +526,6 @@
           <t>非机动车道宽度</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>根据映射后的道路等级填充，映射关系详见《路网字段属性映射关系》</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -578,11 +543,6 @@
           <t>机非分隔</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>已有的数据保留，空白的地方根据映射后的道路等级填充，映射关系详见《路网字段属性映射关系》</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -600,11 +560,6 @@
           <t>道路等级</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>根据link_type_与isLink判断，根据映射关系进行道路等级名称替换，映射关系详见《路网字段属性映射关系》</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -622,11 +577,6 @@
           <t>道路名称</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>原数据保留，无数据的用link_id替换空白</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -644,11 +594,6 @@
           <t>geometry</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>excel中保留原数据，形成shp则需要利用geopandas替换该列数据为实际的矢量数据</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -662,11 +607,6 @@
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>仅用于进行参数计算的属性，不输出至最终的文件中</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
